--- a/data/test_customers_runtime.xlsx
+++ b/data/test_customers_runtime.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,6 +430,23 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>neyrouz t</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>neyrouz@gmail.com</t>
         </is>
       </c>
     </row>
